--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/Panel-28/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.82584</v>
+        <v>16.94477</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77324</v>
+        <v>16.47775</v>
       </c>
       <c r="E2" t="n">
-        <v>16.44497</v>
+        <v>16.848</v>
       </c>
       <c r="F2" t="n">
-        <v>42.85298</v>
+        <v>42.46333</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05114</v>
+        <v>0.0507</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85109</v>
+        <v>1.7997</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.11028</v>
+        <v>16.79372</v>
       </c>
       <c r="D3" t="n">
-        <v>16.37156</v>
+        <v>16.65686</v>
       </c>
       <c r="E3" t="n">
-        <v>17.21785</v>
+        <v>16.79105</v>
       </c>
       <c r="F3" t="n">
-        <v>42.57885</v>
+        <v>43.0717</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05171</v>
+        <v>0.05094</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85685</v>
+        <v>1.83485</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.79627</v>
+        <v>16.97276</v>
       </c>
       <c r="D4" t="n">
-        <v>16.72521</v>
+        <v>16.61667</v>
       </c>
       <c r="E4" t="n">
-        <v>16.43371</v>
+        <v>16.88823</v>
       </c>
       <c r="F4" t="n">
-        <v>42.95835</v>
+        <v>43.01759</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05037</v>
+        <v>0.05164</v>
       </c>
       <c r="H4" t="n">
-        <v>1.85017</v>
+        <v>1.82946</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.84013</v>
+        <v>16.83154</v>
       </c>
       <c r="D6" t="n">
-        <v>15.96782</v>
+        <v>16.20477</v>
       </c>
       <c r="E6" t="n">
-        <v>16.86403</v>
+        <v>16.30864</v>
       </c>
       <c r="F6" t="n">
-        <v>21.86366</v>
+        <v>22.29522</v>
       </c>
       <c r="G6" t="n">
-        <v>35.53022</v>
+        <v>34.56858</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81871</v>
+        <v>17.12816</v>
       </c>
       <c r="D7" t="n">
-        <v>16.00242</v>
+        <v>16.08824</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50738</v>
+        <v>16.57186</v>
       </c>
       <c r="F7" t="n">
-        <v>22.0007</v>
+        <v>21.54311</v>
       </c>
       <c r="G7" t="n">
-        <v>34.3357</v>
+        <v>34.34648</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.50132</v>
+        <v>17.06886</v>
       </c>
       <c r="D8" t="n">
-        <v>15.83264</v>
+        <v>16.19757</v>
       </c>
       <c r="E8" t="n">
-        <v>16.46887</v>
+        <v>16.76485</v>
       </c>
       <c r="F8" t="n">
-        <v>21.90677</v>
+        <v>21.58129</v>
       </c>
       <c r="G8" t="n">
-        <v>33.86218</v>
+        <v>34.53896</v>
       </c>
     </row>
   </sheetData>
